--- a/e2e/fixtures/bookings-mixed.xlsx
+++ b/e2e/fixtures/bookings-mixed.xlsx
@@ -76,10 +76,10 @@
     <t>marisol.reyes@example.com</t>
   </si>
   <si>
-    <t>2026-09-12T09:00:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-09-12T17:00:00.000Z</t>
+    <t>2026-09-12T01:00:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-09-12T10:00:00.000Z</t>
   </si>
   <si>
     <t>Reyes Wedding - Tagaytay</t>
